--- a/diseases/d015/2010-2014.xlsx
+++ b/diseases/d015/2010-2014.xlsx
@@ -4469,11 +4469,11 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0002175476800637262</v>
+        <v>0.0002194169360619049</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -5357,11 +5357,11 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.000362579466772877</v>
+        <v>0.0003656948934365081</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -6097,11 +6097,11 @@
         <v>31</v>
       </c>
       <c r="R38" t="n">
-        <v>0.009150172524845838</v>
+        <v>0.009226566700085728</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6985,11 +6985,11 @@
         <v>41</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007132811653226284</v>
+        <v>0.007192363018177063</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7725,11 +7725,11 @@
         <v>24</v>
       </c>
       <c r="R49" t="n">
-        <v>0.00172916646138819</v>
+        <v>0.001743603155921712</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8465,11 +8465,11 @@
         <v>13</v>
       </c>
       <c r="R54" t="n">
-        <v>0.001657117858830348</v>
+        <v>0.001670953024424974</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9205,11 +9205,11 @@
         <v>6</v>
       </c>
       <c r="R59" t="n">
-        <v>0.00115277764092546</v>
+        <v>0.001162402103947808</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -10093,11 +10093,11 @@
         <v>6</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0001440972051156825</v>
+        <v>0.000145300262993476</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10833,11 +10833,11 @@
         <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>7.204860255784125e-05</v>
+        <v>7.265013149673801e-05</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11573,11 +11573,11 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0001440972051156825</v>
+        <v>0.000145300262993476</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -12461,11 +12461,11 @@
         <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>0.0001440972051156825</v>
+        <v>0.000145300262993476</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13201,11 +13201,11 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>7.204860255784125e-05</v>
+        <v>7.265013149673801e-05</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14089,11 +14089,11 @@
         <v>4</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0006484374230205712</v>
+        <v>0.0006538511834706421</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14829,11 +14829,11 @@
         <v>4</v>
       </c>
       <c r="R97" t="n">
-        <v>0.001368923448598984</v>
+        <v>0.001380352498438022</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">

--- a/diseases/d015/2010-2014.xlsx
+++ b/diseases/d015/2010-2014.xlsx
@@ -4476,6 +4476,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5369,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6114,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7007,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7752,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8497,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9242,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10135,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +10880,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11625,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12518,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13263,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14156,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14834,6 +14899,11 @@
       <c r="S97" t="inlineStr">
         <is>
           <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">

--- a/diseases/d015/2010-2014.xlsx
+++ b/diseases/d015/2010-2014.xlsx
@@ -776,28 +776,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -924,28 +938,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1072,28 +1100,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1220,28 +1262,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1368,28 +1424,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1516,28 +1586,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1664,28 +1748,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1812,28 +1910,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -1960,28 +2072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2108,28 +2234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2256,28 +2396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -2404,28 +2558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2552,28 +2720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -2700,28 +2882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -2848,28 +3044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -2996,28 +3206,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3144,28 +3368,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -3292,28 +3530,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -3440,28 +3692,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -3588,28 +3854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -3736,28 +4016,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -3884,28 +4178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -4032,28 +4340,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -4180,28 +4502,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -4328,28 +4664,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -4629,28 +4979,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -4777,28 +5141,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -4925,28 +5303,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -5073,28 +5465,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -5221,28 +5627,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -5522,28 +5942,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -5670,28 +6104,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -5818,28 +6266,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -5966,28 +6428,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -6267,28 +6743,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6415,28 +6905,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6563,28 +7067,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -6711,28 +7229,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -6859,28 +7391,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -7160,28 +7706,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -7308,28 +7868,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -7456,28 +8030,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -7604,28 +8192,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -7905,28 +8507,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -8053,28 +8669,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -8201,28 +8831,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -8349,28 +8993,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8650,28 +9308,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -8798,28 +9470,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -8946,28 +9632,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -9094,28 +9794,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -9395,28 +10109,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -9543,28 +10271,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -9691,28 +10433,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -9839,28 +10595,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -9987,28 +10757,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -10288,28 +11072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -10436,28 +11234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -10584,28 +11396,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -10732,28 +11558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -11033,28 +11873,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -11181,28 +12035,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -11329,28 +12197,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -11477,28 +12359,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -11778,28 +12674,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -11926,28 +12836,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -12074,28 +12998,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -12222,28 +13160,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -12370,28 +13322,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -12671,28 +13637,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -12819,28 +13799,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -12967,28 +13961,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -13115,28 +14123,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -13416,28 +14438,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -13564,28 +14600,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -13712,28 +14762,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -13860,28 +14924,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -14008,28 +15086,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -14309,28 +15401,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -14457,28 +15563,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -14605,28 +15725,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -14753,28 +15887,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -15054,28 +16202,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -15202,28 +16364,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -15350,28 +16526,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -15498,28 +16688,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">

--- a/diseases/d015/2010-2014.xlsx
+++ b/diseases/d015/2010-2014.xlsx
@@ -4821,11 +4821,6 @@
       <c r="R27" t="n">
         <v>0.0002194169360619049</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4838,22 +4833,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5784,11 +5769,6 @@
       <c r="R33" t="n">
         <v>0.0003656948934365081</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5801,22 +5781,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -6585,11 +6555,6 @@
       <c r="R38" t="n">
         <v>0.009226566700085728</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,22 +6567,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -7548,11 +7503,6 @@
       <c r="R44" t="n">
         <v>0.007192363018177063</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7565,22 +7515,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -8349,11 +8289,6 @@
       <c r="R49" t="n">
         <v>0.001743603155921712</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8366,22 +8301,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -9150,11 +9075,6 @@
       <c r="R54" t="n">
         <v>0.001670953024424974</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9167,22 +9087,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9951,11 +9861,6 @@
       <c r="R59" t="n">
         <v>0.001162402103947808</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9968,22 +9873,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -10914,11 +10809,6 @@
       <c r="R65" t="n">
         <v>0.000145300262993476</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10931,22 +10821,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11715,11 +11595,6 @@
       <c r="R70" t="n">
         <v>7.265013149673801e-05</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11732,22 +11607,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -12516,11 +12381,6 @@
       <c r="R75" t="n">
         <v>0.000145300262993476</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12533,22 +12393,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -13479,11 +13329,6 @@
       <c r="R81" t="n">
         <v>0.000145300262993476</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13496,22 +13341,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -14280,11 +14115,6 @@
       <c r="R86" t="n">
         <v>7.265013149673801e-05</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14297,22 +14127,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -15243,11 +15063,6 @@
       <c r="R92" t="n">
         <v>0.0006538511834706421</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15260,22 +15075,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -16044,11 +15849,6 @@
       <c r="R97" t="n">
         <v>0.001380352498438022</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16061,22 +15861,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>

--- a/diseases/d015/2010-2014.xlsx
+++ b/diseases/d015/2010-2014.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -783,7 +781,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -793,12 +791,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -808,11 +801,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -927,17 +915,15 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -945,7 +931,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -955,12 +941,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -970,11 +951,6 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1089,17 +1065,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1107,7 +1081,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1117,12 +1091,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1132,11 +1101,6 @@
       </c>
       <c r="AT4" t="n">
         <v>1</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1251,17 +1215,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1269,7 +1231,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1279,12 +1241,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1294,11 +1251,6 @@
       </c>
       <c r="AT5" t="n">
         <v>1</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1413,17 +1365,15 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1431,7 +1381,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1441,12 +1391,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1456,11 +1401,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1575,17 +1515,15 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1593,7 +1531,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1603,12 +1541,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1618,11 +1551,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1737,17 +1665,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1755,7 +1681,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1765,12 +1691,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1780,11 +1701,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1899,17 +1815,15 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -1917,7 +1831,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1927,12 +1841,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -1942,11 +1851,6 @@
       </c>
       <c r="AT9" t="n">
         <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2061,17 +1965,15 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2079,7 +1981,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2089,12 +1991,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2104,11 +2001,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2223,17 +2115,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2241,7 +2131,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2251,12 +2141,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2266,11 +2151,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2385,17 +2265,15 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2403,7 +2281,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2413,12 +2291,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2428,11 +2301,6 @@
       </c>
       <c r="AT12" t="n">
         <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2547,17 +2415,15 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2565,7 +2431,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2575,12 +2441,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2590,11 +2451,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2709,17 +2565,15 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2727,7 +2581,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2737,12 +2591,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2752,11 +2601,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2871,17 +2715,15 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -2889,7 +2731,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2899,12 +2741,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2914,11 +2751,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3033,17 +2865,15 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3051,7 +2881,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -3061,12 +2891,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -3076,11 +2901,6 @@
       </c>
       <c r="AT16" t="n">
         <v>1</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3195,17 +3015,15 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3213,7 +3031,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3223,12 +3041,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3238,11 +3051,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3357,17 +3165,15 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3375,7 +3181,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3385,12 +3191,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -3400,11 +3201,6 @@
       </c>
       <c r="AT18" t="n">
         <v>1</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3519,17 +3315,15 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3537,7 +3331,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3547,12 +3341,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -3562,11 +3351,6 @@
       </c>
       <c r="AT19" t="n">
         <v>1</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3681,17 +3465,15 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3699,7 +3481,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3709,12 +3491,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -3724,11 +3501,6 @@
       </c>
       <c r="AT20" t="n">
         <v>1</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3843,17 +3615,15 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -3861,7 +3631,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3871,12 +3641,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -3886,11 +3651,6 @@
       </c>
       <c r="AT21" t="n">
         <v>1</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4005,17 +3765,15 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4023,7 +3781,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4033,12 +3791,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -4048,11 +3801,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4167,17 +3915,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4185,7 +3931,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4195,12 +3941,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -4210,11 +3951,6 @@
       </c>
       <c r="AT23" t="n">
         <v>1</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4329,17 +4065,15 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4347,7 +4081,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4357,12 +4091,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4372,11 +4101,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4491,17 +4215,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4509,7 +4231,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4519,12 +4241,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4534,11 +4251,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4653,17 +4365,15 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4671,7 +4381,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4681,12 +4391,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4696,11 +4401,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4953,17 +4653,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -4971,7 +4669,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4981,12 +4679,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -4996,11 +4689,6 @@
       </c>
       <c r="AT28" t="n">
         <v>1</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5115,17 +4803,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -5133,7 +4819,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -5143,12 +4829,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -5158,11 +4839,6 @@
       </c>
       <c r="AT29" t="n">
         <v>1</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5277,17 +4953,15 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -5295,7 +4969,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5305,12 +4979,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -5320,11 +4989,6 @@
       </c>
       <c r="AT30" t="n">
         <v>1</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5439,17 +5103,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -5457,7 +5119,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5467,12 +5129,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -5482,11 +5139,6 @@
       </c>
       <c r="AT31" t="n">
         <v>1</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5601,17 +5253,15 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -5619,7 +5269,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5629,12 +5279,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -5644,11 +5289,6 @@
       </c>
       <c r="AT32" t="n">
         <v>1</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5901,17 +5541,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -5919,7 +5557,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5929,12 +5567,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -5944,11 +5577,6 @@
       </c>
       <c r="AT34" t="n">
         <v>1</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6063,17 +5691,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -6081,7 +5707,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6091,12 +5717,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -6106,11 +5727,6 @@
       </c>
       <c r="AT35" t="n">
         <v>1</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6225,17 +5841,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -6243,7 +5857,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -6253,12 +5867,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -6268,11 +5877,6 @@
       </c>
       <c r="AT36" t="n">
         <v>1</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6387,17 +5991,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -6405,7 +6007,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6415,12 +6017,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -6430,11 +6027,6 @@
       </c>
       <c r="AT37" t="n">
         <v>1</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6687,17 +6279,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -6705,7 +6295,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6715,12 +6305,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -6730,11 +6315,6 @@
       </c>
       <c r="AT39" t="n">
         <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6849,17 +6429,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -6867,7 +6445,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6877,12 +6455,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -6892,11 +6465,6 @@
       </c>
       <c r="AT40" t="n">
         <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7011,17 +6579,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7029,7 +6595,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -7039,12 +6605,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -7054,11 +6615,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7173,17 +6729,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7191,7 +6745,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -7201,12 +6755,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -7216,11 +6765,6 @@
       </c>
       <c r="AT42" t="n">
         <v>1</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7335,17 +6879,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7353,7 +6895,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7363,12 +6905,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -7378,11 +6915,6 @@
       </c>
       <c r="AT43" t="n">
         <v>1</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7635,17 +7167,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7653,7 +7183,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7663,12 +7193,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
@@ -7678,11 +7203,6 @@
       </c>
       <c r="AT45" t="n">
         <v>1</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7797,17 +7317,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7815,7 +7333,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7825,12 +7343,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -7840,11 +7353,6 @@
       </c>
       <c r="AT46" t="n">
         <v>1</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7959,17 +7467,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -7977,7 +7483,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7987,12 +7493,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -8002,11 +7503,6 @@
       </c>
       <c r="AT47" t="n">
         <v>1</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8121,17 +7617,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -8139,7 +7633,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -8149,12 +7643,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -8164,11 +7653,6 @@
       </c>
       <c r="AT48" t="n">
         <v>1</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8421,17 +7905,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -8439,7 +7921,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8449,12 +7931,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -8464,11 +7941,6 @@
       </c>
       <c r="AT50" t="n">
         <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8583,17 +8055,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -8601,7 +8071,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8611,12 +8081,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -8626,11 +8091,6 @@
       </c>
       <c r="AT51" t="n">
         <v>1</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8745,17 +8205,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -8763,7 +8221,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8773,12 +8231,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -8788,11 +8241,6 @@
       </c>
       <c r="AT52" t="n">
         <v>1</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8907,17 +8355,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -8925,7 +8371,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8935,12 +8381,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -8950,11 +8391,6 @@
       </c>
       <c r="AT53" t="n">
         <v>1</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9207,17 +8643,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -9225,7 +8659,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9235,12 +8669,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -9250,11 +8679,6 @@
       </c>
       <c r="AT55" t="n">
         <v>1</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9369,17 +8793,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -9387,7 +8809,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9397,12 +8819,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
@@ -9412,11 +8829,6 @@
       </c>
       <c r="AT56" t="n">
         <v>1</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9531,17 +8943,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -9549,7 +8959,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9559,12 +8969,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
@@ -9574,11 +8979,6 @@
       </c>
       <c r="AT57" t="n">
         <v>1</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9693,17 +9093,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -9711,7 +9109,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9721,12 +9119,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
@@ -9736,11 +9129,6 @@
       </c>
       <c r="AT58" t="n">
         <v>1</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9993,17 +9381,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10011,7 +9397,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -10021,12 +9407,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
@@ -10036,11 +9417,6 @@
       </c>
       <c r="AT60" t="n">
         <v>1</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -10155,17 +9531,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10173,7 +9547,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10183,12 +9557,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ61" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
@@ -10198,11 +9567,6 @@
       </c>
       <c r="AT61" t="n">
         <v>1</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10317,17 +9681,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10335,7 +9697,7 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -10345,12 +9707,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -10360,11 +9717,6 @@
       </c>
       <c r="AT62" t="n">
         <v>1</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10479,17 +9831,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10497,7 +9847,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -10507,12 +9857,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ63" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
@@ -10522,11 +9867,6 @@
       </c>
       <c r="AT63" t="n">
         <v>1</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10641,17 +9981,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10659,7 +9997,7 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10669,12 +10007,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ64" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
@@ -10684,11 +10017,6 @@
       </c>
       <c r="AT64" t="n">
         <v>1</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10941,17 +10269,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -10959,7 +10285,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10969,12 +10295,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
@@ -10984,11 +10305,6 @@
       </c>
       <c r="AT66" t="n">
         <v>1</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -11103,17 +10419,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -11121,7 +10435,7 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -11131,12 +10445,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
@@ -11146,11 +10455,6 @@
       </c>
       <c r="AT67" t="n">
         <v>1</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11265,17 +10569,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -11283,7 +10585,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11293,12 +10595,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
@@ -11308,11 +10605,6 @@
       </c>
       <c r="AT68" t="n">
         <v>1</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11427,17 +10719,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -11445,7 +10735,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11455,12 +10745,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
@@ -11470,11 +10755,6 @@
       </c>
       <c r="AT69" t="n">
         <v>1</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11727,17 +11007,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -11745,7 +11023,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11755,12 +11033,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ71" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
@@ -11770,11 +11043,6 @@
       </c>
       <c r="AT71" t="n">
         <v>1</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11889,17 +11157,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U72" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -11907,7 +11173,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11917,12 +11183,7 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
@@ -11932,11 +11193,6 @@
       </c>
       <c r="AT72" t="n">
         <v>1</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -12051,17 +11307,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -12069,7 +11323,7 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -12079,12 +11333,7 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
@@ -12094,11 +11343,6 @@
       </c>
       <c r="AT73" t="n">
         <v>1</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -12213,17 +11457,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -12231,7 +11473,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -12241,12 +11483,7 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
@@ -12256,11 +11493,6 @@
       </c>
       <c r="AT74" t="n">
         <v>1</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12513,17 +11745,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -12531,7 +11761,7 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12541,12 +11771,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
@@ -12556,11 +11781,6 @@
       </c>
       <c r="AT76" t="n">
         <v>1</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12675,17 +11895,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -12693,7 +11911,7 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12703,12 +11921,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
@@ -12718,11 +11931,6 @@
       </c>
       <c r="AT77" t="n">
         <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12837,17 +12045,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U78" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -12855,7 +12061,7 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -12865,12 +12071,7 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
@@ -12880,11 +12081,6 @@
       </c>
       <c r="AT78" t="n">
         <v>1</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12999,17 +12195,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U79" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13017,7 +12211,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -13027,12 +12221,7 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
@@ -13042,11 +12231,6 @@
       </c>
       <c r="AT79" t="n">
         <v>1</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -13161,17 +12345,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13179,7 +12361,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -13189,12 +12371,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
@@ -13204,11 +12381,6 @@
       </c>
       <c r="AT80" t="n">
         <v>1</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -13461,17 +12633,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U82" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13479,7 +12649,7 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -13489,12 +12659,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
@@ -13504,11 +12669,6 @@
       </c>
       <c r="AT82" t="n">
         <v>1</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13623,17 +12783,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U83" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13641,7 +12799,7 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13651,12 +12809,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr">
@@ -13666,11 +12819,6 @@
       </c>
       <c r="AT83" t="n">
         <v>1</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13785,17 +12933,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U84" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13803,7 +12949,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -13813,12 +12959,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr">
@@ -13828,11 +12969,6 @@
       </c>
       <c r="AT84" t="n">
         <v>1</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13947,17 +13083,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U85" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -13965,7 +13099,7 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -13975,12 +13109,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr">
@@ -13990,11 +13119,6 @@
       </c>
       <c r="AT85" t="n">
         <v>1</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -14247,17 +13371,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -14265,7 +13387,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14275,12 +13397,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
@@ -14290,11 +13407,6 @@
       </c>
       <c r="AT87" t="n">
         <v>1</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14409,17 +13521,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U88" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -14427,7 +13537,7 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -14437,12 +13547,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
@@ -14452,11 +13557,6 @@
       </c>
       <c r="AT88" t="n">
         <v>1</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14571,17 +13671,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -14589,7 +13687,7 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -14599,12 +13697,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
@@ -14614,11 +13707,6 @@
       </c>
       <c r="AT89" t="n">
         <v>1</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14733,17 +13821,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -14751,7 +13837,7 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -14761,12 +13847,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
@@ -14776,11 +13857,6 @@
       </c>
       <c r="AT90" t="n">
         <v>1</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14895,17 +13971,15 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -14913,7 +13987,7 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -14923,12 +13997,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -14938,11 +14007,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -15195,17 +14259,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U93" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -15213,7 +14275,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -15223,12 +14285,7 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ93" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
@@ -15238,11 +14295,6 @@
       </c>
       <c r="AT93" t="n">
         <v>1</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -15357,17 +14409,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U94" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -15375,7 +14425,7 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15385,12 +14435,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
@@ -15400,11 +14445,6 @@
       </c>
       <c r="AT94" t="n">
         <v>1</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15519,17 +14559,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -15537,7 +14575,7 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -15547,12 +14585,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -15562,11 +14595,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15681,17 +14709,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -15699,7 +14725,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -15709,12 +14735,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -15724,11 +14745,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15981,17 +14997,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -15999,7 +15013,7 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -16009,12 +15023,7 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
@@ -16024,11 +15033,6 @@
       </c>
       <c r="AT98" t="n">
         <v>1</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -16143,17 +15147,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -16161,7 +15163,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -16171,12 +15173,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -16186,11 +15183,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -16305,17 +15297,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -16323,7 +15313,7 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -16333,12 +15323,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -16348,11 +15333,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16467,17 +15447,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_a3849536bf05c1aa8387e4bc9da1</t>
@@ -16485,7 +15463,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -16495,12 +15473,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -16510,11 +15483,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
